--- a/ALL/A1-Pinterest_01-out/images.xlsx
+++ b/ALL/A1-Pinterest_01-out/images.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,76 @@
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>error_ing</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Statut Article</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>article_title</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_article</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_title</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>recipe_title_pin</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_description</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_keywords</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>_yoast_wpseo_focuskw</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>_yoast_wpseo_metadesc</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>_yoast_wpseo_keywordsynonyms</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_image</t>
         </is>
       </c>
     </row>
@@ -627,6 +697,166 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Creamy Garlic Spinach Pasta: A Delicious Italian Delight
+## Introduction
+Creamy Garlic Spinach Pasta is a dish that perfectly encapsulates the essence of Italian cooking—simple ingredients coming together to create something extraordinary. The combination of al dente fettuccine, fresh spinach, savory garlic, and a rich cream sauce offers a satisfying meal that is both comforting and elegant. This dish is versatile enough for casual weeknight dinners yet sophisticated enough to impress guests at a dinner party.
+As you dive into this recipe, you’ll discover how the vivid green of fresh spinach and the creamy sauce create a visually appealing presentation that is sure to entice. The flavor profile is wonderfully balanced, with the garlic providing a warm, aromatic quality while the Parmesan cheese brings a salty nuttiness that complements the rich cream beautifully. It's the kind of dish that warms the heart and delights the palate, making it a favorite for pasta enthusiasts.
+Whether it’s a rainy evening or a sunny afternoon, this Creamy Garlic Spinach Pasta is a perfect choice. It's quick to prepare, requiring just 10 minutes of prep time and 15 minutes of cooking, making it an excellent option for those busy days when you still want to enjoy a homemade meal. 
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 15 minutes
+- Total Time: 25 minutes
+- Course: Main Course
+- Cuisine: Italian
+- Servings: 4
+- Calories: ~450 per serving
+Creamy Garlic Spinach Pasta is a delightful main course that features fettuccine tossed in a rich and creamy garlic spinach sauce. This recipe balances the savory flavors of garlic and Parmesan cheese with the freshness of spinach, making it a go-to for pasta lovers.
+### Cooking Philosophy
+At the core of Italian cooking is a philosophy of simplicity—a few quality ingredients can yield extraordinary results. This recipe exemplifies that principle, showcasing how the richness of cream, the sweetness of sautéed garlic, and the earthy taste of fresh spinach come together in perfect harmony. Fettuccine, with its flat shape, serves as an ideal vessel for the creamy sauce, ensuring each bite is filled with flavor. This approach not only highlights individual ingredients but also emphasizes the joy of cooking, where the act itself becomes a celebration.
+### Nutritional Highlights
+This luxurious pasta dish may seem indulgent, but it remains a balanced option for a main course. Each serving contains approximately 450 calories, allowing you to enjoy this rich dish while still keeping an eye on nutritional intake. With fresh spinach providing essential vitamins and minerals, this pasta could not only satisfy your cravings but also offer some health benefits—a testament to the idea that comfort food can also be wholesome.
+## Ingredients
+### To prepare Creamy Garlic Spinach Pasta, gather the following ingredients:
+- 8 oz fettuccine pasta
+- 2 cups fresh spinach
+- 3 cloves garlic, minced
+- 1 cup heavy cream
+- 1/2 cup grated Parmesan cheese
+- 2 tbsp olive oil
+- Salt and pepper to taste
+- Red pepper flakes (optional)
+Each ingredient plays a vital role in constructing the flavor profile of the dish. The fettuccine forms the base, while the fresh spinach adds color and nutrients. Garlic brings depth with its sharp, aromatic essence, and the heavy cream forms the luscious sauce that binds everything together. The Parmesan cheese contributes creaminess and a salty kick, making it indispensable. Optional red pepper flakes can add just the right amount of heat if you choose.
+{{image_ing_1}}
+## Instructions
+### Detailed instructions ensure a successful cooking experience:
+1. Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.
+2. In a large skillet, heat the olive oil over medium heat. Add the minced garlic and sauté for about 1 minute until fragrant.
+3. Add the fresh spinach to the skillet and cook until wilted, about 2-3 minutes.
+4. Pour in the heavy cream and bring to a gentle simmer. Stir well to combine.
+5. Add the grated Parmesan cheese and mix until melted and creamy. Season with salt, pepper, and red pepper flakes if using.
+6. Toss the cooked fettuccine in the creamy spinach sauce until well coated.
+7. Serve immediately, garnished with extra Parmesan cheese if desired.
+### Cooking the Fettuccine
+Begin by boiling water and cooking the fettuccine pasta until al dente. Proper cooking time is crucial for perfect texture. Fettuccine should be firm to the bite, which allows it to hold up against the rich sauce. Once cooked, drain the pasta, taking care to reserve a little of the pasta water, as it can be useful for adjusting the sauce’s consistency later.
+### Sautéing the Garlic
+Using olive oil, sauté the minced garlic over medium heat. This step releases the garlic's natural oils, creating a fragrant base for the sauce. Be cautious to avoid burning the garlic, as it can turn bitter; a minute should be sufficient to bring out its aromatic qualities.
+### Incorporating Spinach
+Once the garlic is fragrant, add fresh spinach to the skillet and cook until wilted. The vibrant green of the spinach not only adds a pop of color but also fills the dish with essential nutrients. The cooking time is short, so keep an eye on the spinach as it wilts quickly, ensuring it retains its bright color.
+### Creating the Creamy Sauce
+Introduce heavy cream into the skillet and bring it to a gentle simmer. This step is vital for developing a rich, creamy sauce. The cream thickens as it heats, becoming velvety and smooth. Stirring continuously ensures that the cream doesn’t separate and combines well with the garlic and spinach.
+### Melting the Cheese
+Incorporate grated Parmesan cheese, ensuring it melts thoroughly for a luxurious texture. Parmesan doesn’t just add creaminess but also depth of flavor, elevating the sauce. Stir until the cheese is fully integrated, creating a cohesive and indulgent sauce that clings beautifully to the pasta.
+### Seasoning the Sauce
+Season the mixture with salt, pepper, and optional red pepper flakes to enhance flavor. The seasoning helps to balance the richness of the cream, and the red pepper flakes can add an exciting kick if desired. Taste the sauce before adding salt, as the Parmesan already contributes some saltiness.
+### Tossing the Pasta
+Combine the cooked fettuccine with the creamy spinach sauce, ensuring each strand is well coated. The pasta absorbs some of the sauce, allowing every bite to be infused with the creamy flavor. If the sauce appears too thick, a splash of reserved pasta water can help loosen it without sacrificing richness.
+### Serving Suggestions
+Serve the pasta immediately, garnished with additional Parmesan cheese if desired. Freshly grated cheese on top adds an enticing finish, and a sprinkle of extra red pepper flakes can please those who enjoy a bit of heat. This dish is best enjoyed fresh, with its bright flavors and comforting texture taking center stage. 
+In the next part of this article, we will cover essential cooking tips to enhance your experience and ensure perfect results every time you prepare this Creamy Garlic Spinach Pasta.
+### A Few Tips Can Elevate Your Cooking Experience
+Making Creamy Garlic Spinach Pasta is a straightforward process, but a few tips can enhance not just the flavor but also your overall cooking experience.
+### Selecting Pasta
+While fettuccine pasta is typically used in this recipe, selecting the right type of pasta can significantly influence your dish's overall texture and flavor absorption. Wider noodles like fettuccine can hold onto the creamy sauce better than thinner varieties. However, if you prefer a different texture, opt for tagliatelle or pappardelle. It's essential to ensure the pasta is cooked al dente as it will continue to cook slightly when tossed with the sauce.
+### Using Fresh Ingredients
+Another crucial factor in creating a delicious pasta dish is the use of fresh ingredients. Fresh spinach lends a bright flavor and vibrant color to your pasta. Dried spinach or frozen alternatives may lack the same textural and flavor profiles. Additionally, using high-quality Parmesan cheese can elevate your dish significantly. Pre-grated cheese often contains anti-caking agents that can alter the texture and flavor. Grating or shaving fresh Parmigiano-Reggiano offers a nutty flavor that complements the creaminess of the sauce perfectly.
+### Adjusting Creaminess
+If you're looking to lighten the dish without sacrificing flavor, consider adjusting the amount of heavy cream or substituting it with a lighter cream alternative such as half and half or a low-fat cream. You can also add a little vegetable broth to create a slightly thinner sauce while still keeping the creamy consistency. However, be cautious not to dilute the flavor too much.
+## Common Mistakes to Avoid
+While preparing Creamy Garlic Spinach Pasta is fairly simple, a few common pitfalls can detract from the overall result.
+### Overcooking the Pasta
+One of the most frequent mistakes is overcooking the pasta. Cooking fettuccine too long results in a mushy texture, which diminishes the appeal of the dish. For perfect al dente pasta, always follow the package instructions and test it a minute or two before the suggested cooking time. This will ensure that your pasta maintains its shape and has the perfect bite.
+### Neglecting the Garlic
+Garlic is a key ingredient in this recipe, and it contributes enormously to the dish's flavor profile. However, burnt garlic can ruin the flavor of the sauce. To avoid this, keep a close watch while sautéing. Once the garlic becomes fragrant and slightly golden, it's time to add the spinach if you want to retain its aromatic properties without burning.
+### Forgetting the Seasoning
+Each step in your cooking process calls for careful attention to seasoning. Undersalting at any point can lead to a bland sauce that lacks depth. Make sure to taste your sauce before serving, and adjust with salt and pepper accordingly. Additionally, adding red pepper flakes not only provides flavor but can also bring a nice kick if desired.
+## Variations and Adaptations
+One of the best things about pasta dishes is their adaptability. You can easily explore different interpretations of the Creamy Garlic Spinach Pasta.
+### Vegetarian Additions
+If you want to enhance your pasta with more depth, consider adding vegetarian options. Sautéed mushrooms provide an earthy flavor that pairs beautifully with the creamy sauce. Sun-dried tomatoes are another excellent addition, offering both sweetness and acidity.
+### Protein Boost
+For those looking to increase the protein content of the dish, grilled chicken or shrimp can be perfect additions. Simply prep your choice of protein, season it to taste, and toss it with the sauce and pasta before serving to create a more filling meal.
+### Gluten-Free Option
+For those with dietary restrictions, using gluten-free pasta is a great alternative. Many options available today replicate the texture and flavor of wheat pasta quite well. Just ensure to cook it according to the package directions, as cooking times may vary.
+## Storage Tips
+To enjoy leftovers from your Creamy Garlic Spinach Pasta, proper storage is essential.
+### Refrigerating Leftovers
+Store leftovers in an airtight container in the fridge for up to two days. To maintain freshness, it's best to refrigerate the sauce and pasta separately if possible. Combine them when you are ready to reheat for the best texture and flavor.
+### Reheating Instructions
+When ready to eat your leftovers, gently reheat them on the stove, adding a splash of cream or milk to maintain the sauce's consistency. This will help revive the creaminess without making the dish too thick or clumpy. Stir occasionally to ensure even heating.
+## Pairing Suggestions
+Enhancing your dining experience goes beyond the main dish; certain pairings can elevate your meal to new heights.
+### Wine Pairings
+A light pinot grigio or a crisp Sauvignon Blanc pairs wonderfully with creamy pasta dishes. These wines have enough acidity to cut through the richness of the cream and cheese, ensuring a balanced palate. 
+### Side Dishes
+Complement your pasta with suitable side dishes. Garlic bread is a classic choice and can soak up the delightful creamy sauce left on your plate. Additionally, a fresh garden salad with a tangy vinaigrette will provide a refreshing contrast to the richness of your main dish.
+## Conclusion
+Creamy Garlic Spinach Pasta is an exquisite Italian dish that combines the richness of cream and Parmesan with the freshness of spinach, creating a perfect balance of flavors and textures. This recipe, with a total cooking time of 25 minutes, is both quick and satisfying, making it an excellent choice for any pasta lover.
+</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Creamy Garlic Spinach Pasta: A Delicious Italian Delight</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Creamy Garlic Spinach Fettuccine Pasta Recipe in 25 Minutes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Creamy Spinach Fettuccine Delight</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Indulge in a deliciously creamy garlic spinach fettuccine pasta recipe that comes together in just 25 minutes. Perfect for a cozy weeknight dinner, this Italian dish features al dente fettuccine tossed with fresh spinach and a rich Parmesan cheese sauce. Elevate your mealtime with this comforting pasta that celebrates the flavors of Italian cuisine.</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Creamy pasta, garlic, spinach, fettuccine, Parmesan cheese, Italian cuisine</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Creamy Garlic Spinach Pasta</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Indulge in creamy garlic spinach pasta that's quick and delicious. Perfect for a comforting Italian dish in just 25 minutes!</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rich Garlic Spinach Noodles, Velvety Spinach Pasta with Garlic, Smooth Garlic Parmesan Spinach Fettuccine</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>../ALL/A1-Pinterest_01-out/output_images\image_1.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
